--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:22</t>
+    <t xml:space="preserve">2026-09-24 01:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -543,7 +543,7 @@
         <v>-0.15</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3">
@@ -554,10 +554,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4">
@@ -571,7 +571,7 @@
         <v>-0.05</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5">
@@ -585,7 +585,7 @@
         <v>0.22</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6">
@@ -599,7 +599,7 @@
         <v>0.26</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7">
@@ -610,10 +610,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8">
@@ -624,10 +624,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -638,10 +638,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -652,10 +652,10 @@
         <v>11</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
@@ -666,10 +666,10 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12">
@@ -680,10 +680,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13">
@@ -694,10 +694,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
@@ -708,10 +708,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15">
@@ -722,10 +722,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16">
@@ -736,10 +736,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17">
@@ -750,10 +750,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18">
@@ -767,7 +767,7 @@
         <v>-0.41</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="19">
@@ -781,7 +781,7 @@
         <v>-0.2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20">
@@ -792,10 +792,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21">
@@ -809,7 +809,7 @@
         <v>0.06</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -820,10 +820,10 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -834,10 +834,10 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_arica_y_parinacota.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:12</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
